--- a/Hand_edited_log/2/StudentsSolution.xlsx
+++ b/Hand_edited_log/2/StudentsSolution.xlsx
@@ -61,76 +61,160 @@
     <x:t>3</x:t>
   </x:si>
   <x:si>
+    <x:t>cuongnmhe182472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ducnthe160854</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungnmhe187141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>halvhe182299</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
     <x:t>hieudmhe182298</x:t>
   </x:si>
   <x:si>
-    <x:t>4</x:t>
+    <x:t>8</x:t>
   </x:si>
   <x:si>
     <x:t>hieudnhe186375</x:t>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hoangpvhe189009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huynqhe180360</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huynqhe181101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>KhaiTTHE180455</x:t>
   </x:si>
   <x:si>
-    <x:t>6</x:t>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kiennthe180530</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t>lamtthe161932</x:t>
   </x:si>
   <x:si>
-    <x:t>7</x:t>
+    <x:t>15</x:t>
   </x:si>
   <x:si>
     <x:t>linhvhhe150945</x:t>
   </x:si>
   <x:si>
-    <x:t>8</x:t>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>longtdhe186919</x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
+    <x:t>17</x:t>
   </x:si>
   <x:si>
     <x:t>luongndhe181876</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
+    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>minhpdhe180520</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>namlthe187066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
   </x:si>
   <x:si>
     <x:t>Phienhdhe181642</x:t>
   </x:si>
   <x:si>
-    <x:t>12</x:t>
+    <x:t>21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quandxhe181250</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>QuanNDHE171155</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quannmhe161255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thangdqhe180102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thanglmhe173199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thanhdhhe180714</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
   </x:si>
   <x:si>
     <x:t>thanhnche171664</x:t>
   </x:si>
   <x:si>
-    <x:t>14</x:t>
+    <x:t>28</x:t>
   </x:si>
   <x:si>
     <x:t>tungbbhe176368</x:t>
   </x:si>
   <x:si>
-    <x:t>15</x:t>
+    <x:t>29</x:t>
   </x:si>
   <x:si>
     <x:t>tuyennvhe186728</x:t>
@@ -504,11 +588,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G16"/>
+  <x:dimension ref="A1:G30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.424911" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17.567768" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="10.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="8.282054" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="10.567768" style="0" customWidth="1"/>
@@ -884,6 +968,328 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" spans="1:7">
+      <x:c r="A17" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:7">
+      <x:c r="A18" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:7">
+      <x:c r="A19" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:7">
+      <x:c r="A20" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:7">
+      <x:c r="A21" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:7">
+      <x:c r="A22" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:7">
+      <x:c r="A23" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:7">
+      <x:c r="A24" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:7">
+      <x:c r="A25" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:7">
+      <x:c r="A26" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:7">
+      <x:c r="A27" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:7">
+      <x:c r="A28" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:7">
+      <x:c r="A29" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:7">
+      <x:c r="A30" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
